--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="89">
   <si>
     <t>Group</t>
   </si>
@@ -126,6 +126,9 @@
     <t>8.2e-05</t>
   </si>
   <si>
+    <t>No.</t>
+  </si>
+  <si>
     <t>Compound (annotation)</t>
   </si>
   <si>
@@ -165,13 +168,16 @@
     <t>Detected, % Control/BC/PC</t>
   </si>
   <si>
+    <t>C19H28O3 oxo-androstane (putatively 11-oxoetiocholanolone)</t>
+  </si>
+  <si>
     <t>unknown</t>
   </si>
   <si>
     <t>Dodecanoylcarnitine</t>
   </si>
   <si>
-    <t>Ethyl 2-amino-5-methyl-3-thiophene</t>
+    <t>Ethyl 2-amino-5-methyl-3-thiophenecarboxylate</t>
   </si>
   <si>
     <t>Biliverdin</t>
@@ -183,7 +189,7 @@
     <t>Valyl-Leucine</t>
   </si>
   <si>
-    <t>C19H28O3 oxo-androstane (putatively 11-oxoetiocholanolone)</t>
+    <t>5.beta.-Androstan-3.alpha.-ol-11,17-dione</t>
   </si>
   <si>
     <t>NCGC00380230-01_C26H40O9_2,4a,6-Trihydroxy-8-isopropyl-1,1-dimethyl-2,3,4,4a,5,10,11,11a-octahydro-1H-dibenzo[a,d][7]annulen-7-yl beta-D-glucopyranoside</t>
@@ -192,9 +198,6 @@
     <t>LAUROYLCARNITINE</t>
   </si>
   <si>
-    <t>Ethyl 2-amino-5-methyl-3-thiophenecarboxylate</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
@@ -207,12 +210,12 @@
     <t>Val-Leu</t>
   </si>
   <si>
-    <t>5.beta.-Androstan-3.alpha.-ol-11,17-dione</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
+    <t>6.3e-03</t>
+  </si>
+  <si>
     <t>1.9e-02</t>
   </si>
   <si>
@@ -234,7 +237,7 @@
     <t>4.8e-02</t>
   </si>
   <si>
-    <t>6.3e-03</t>
+    <t>0.000</t>
   </si>
   <si>
     <t>0.011</t>
@@ -256,9 +259,6 @@
   </si>
   <si>
     <t>0.004</t>
-  </si>
-  <si>
-    <t>0.000</t>
   </si>
   <si>
     <t>0.025</t>
@@ -786,10 +786,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -829,333 +829,360 @@
       <c r="M1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="N1" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2">
+        <v>287.2007</v>
+      </c>
+      <c r="E2">
+        <v>11.06</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>1.25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2">
+        <v>0.8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>541.2642</v>
+      </c>
+      <c r="E3">
+        <v>11.06</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>1.14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3">
+        <v>0.71</v>
+      </c>
+      <c r="L3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4">
+        <v>344.2797</v>
+      </c>
+      <c r="E4">
+        <v>14.37</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>0.93</v>
+      </c>
+      <c r="J4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4">
+        <v>0.73</v>
+      </c>
+      <c r="L4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5">
+        <v>158.027</v>
+      </c>
+      <c r="E5">
+        <v>1.42</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>-1.19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5">
+        <v>0.28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>558.2914</v>
+      </c>
+      <c r="E6">
+        <v>10.76</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>0.87</v>
+      </c>
+      <c r="J6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7">
+        <v>583.2553</v>
+      </c>
+      <c r="E7">
+        <v>13.48</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>2.18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7">
+        <v>0.77</v>
+      </c>
+      <c r="L7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>496.3397</v>
+      </c>
+      <c r="E8">
+        <v>16.71</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8">
+        <v>0.79</v>
+      </c>
+      <c r="L8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>56</v>
       </c>
-      <c r="C2">
-        <v>541.2642</v>
-      </c>
-      <c r="D2">
-        <v>11.06</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9">
+        <v>231.1704</v>
+      </c>
+      <c r="E9">
+        <v>3.72</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
         <v>64</v>
       </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>1.14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2">
-        <v>0.71</v>
-      </c>
-      <c r="K2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3">
-        <v>344.2797</v>
-      </c>
-      <c r="D3">
-        <v>14.37</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3">
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="H3">
-        <v>0.93</v>
-      </c>
-      <c r="I3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3">
-        <v>0.73</v>
-      </c>
-      <c r="K3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4">
-        <v>158.027</v>
-      </c>
-      <c r="D4">
-        <v>1.42</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>-1.19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4">
-        <v>0.28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L4" t="s">
-        <v>82</v>
-      </c>
-      <c r="M4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5">
-        <v>558.2914</v>
-      </c>
-      <c r="D5">
-        <v>10.76</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>0.87</v>
-      </c>
-      <c r="I5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L5" t="s">
-        <v>83</v>
-      </c>
-      <c r="M5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>583.2553</v>
-      </c>
-      <c r="D6">
-        <v>13.48</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>2.18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6">
-        <v>0.77</v>
-      </c>
-      <c r="K6" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>496.3397</v>
-      </c>
-      <c r="D7">
-        <v>16.71</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>1.3</v>
-      </c>
-      <c r="I7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7">
-        <v>0.79</v>
-      </c>
-      <c r="K7" t="s">
-        <v>78</v>
-      </c>
-      <c r="L7" t="s">
-        <v>80</v>
-      </c>
-      <c r="M7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8">
-        <v>231.1704</v>
-      </c>
-      <c r="D8">
-        <v>3.72</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
+      <c r="I9">
         <v>1.72</v>
       </c>
-      <c r="I8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8">
+      <c r="J9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9">
         <v>0.76</v>
-      </c>
-      <c r="K8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9">
-        <v>287.2007</v>
-      </c>
-      <c r="D9">
-        <v>11.06</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-      <c r="H9">
-        <v>1.25</v>
-      </c>
-      <c r="I9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9">
-        <v>0.8</v>
-      </c>
-      <c r="K9" t="s">
-        <v>80</v>
       </c>
       <c r="L9" t="s">
         <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="N9" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
   <si>
     <t>Group</t>
   </si>
@@ -72,6 +72,12 @@
     <t>70 (62–86)</t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Age was not available for 4 participants (4 Control) and sex for 2 (2 Control); 0 lacked both. These participants were retained in the unadjusted analyses (Mann–Whitney U tests, contamination index, cross-validated models on all samples) and excluded from the adjusted linear model (complete-case analysis, n = 88 of 94) and from age- and contamination-matched pairs; missing values were not imputed.</t>
+  </si>
+  <si>
     <t>test</t>
   </si>
   <si>
@@ -150,6 +156,9 @@
     <t>MSI level</t>
   </si>
   <si>
+    <t>Isomers not excluded</t>
+  </si>
+  <si>
     <t>log2FC (adjusted)</t>
   </si>
   <si>
@@ -171,15 +180,12 @@
     <t>C19H28O3 oxo-androstane (putatively 11-oxoetiocholanolone)</t>
   </si>
   <si>
-    <t>unknown</t>
+    <t>Tetrahydrocortisone glucuronide (putative)</t>
   </si>
   <si>
     <t>Dodecanoylcarnitine</t>
   </si>
   <si>
-    <t>Ethyl 2-amino-5-methyl-3-thiophenecarboxylate</t>
-  </si>
-  <si>
     <t>Biliverdin</t>
   </si>
   <si>
@@ -213,6 +219,30 @@
     <t>yes</t>
   </si>
   <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>C19H28O3 steroid isomers (e.g., 11-oxoetiocholanolone, 11-oxoandrosterone, 7β-hydroxy-DHEA) not resolved</t>
+  </si>
+  <si>
+    <t>tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min</t>
+  </si>
+  <si>
+    <t>branched-chain C12 acylcarnitine isomers not excluded</t>
+  </si>
+  <si>
+    <t>tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min</t>
+  </si>
+  <si>
+    <t>biliverdin IXα assumed; other IX isomers not resolved</t>
+  </si>
+  <si>
+    <t>sn-1/sn-2 regioisomers not resolved</t>
+  </si>
+  <si>
+    <t>Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
+  </si>
+  <si>
     <t>6.3e-03</t>
   </si>
   <si>
@@ -222,9 +252,6 @@
     <t>2.0e-02</t>
   </si>
   <si>
-    <t>2.3e-02</t>
-  </si>
-  <si>
     <t>2.9e-02</t>
   </si>
   <si>
@@ -246,9 +273,6 @@
     <t>0.045</t>
   </si>
   <si>
-    <t>0.016</t>
-  </si>
-  <si>
     <t>0.006</t>
   </si>
   <si>
@@ -264,9 +288,6 @@
     <t>0.025</t>
   </si>
   <si>
-    <t>0.010</t>
-  </si>
-  <si>
     <t>0.019</t>
   </si>
   <si>
@@ -283,6 +304,9 @@
   </si>
   <si>
     <t>98/100/100</t>
+  </si>
+  <si>
+    <t>Isomers: C19H28O3 oxo-androstane (putatively 11-oxoetiocholanolone): C19H28O3 steroid isomers (e.g., 11-oxoetiocholanolone, 11-oxoandrosterone, 7β-hydroxy-DHEA) not resolved; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min; Dodecanoylcarnitine: branched-chain C12 acylcarnitine isomers not excluded; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min; Biliverdin: biliverdin IXα assumed; other IX isomers not resolved; LysoPC(16:0): sn-1/sn-2 regioisomers not resolved; Valyl-Leucine: Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
   </si>
 </sst>
 </file>
@@ -614,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -695,6 +719,16 @@
       </c>
       <c r="F4">
         <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -709,74 +743,74 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -786,62 +820,65 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>51</v>
+      </c>
+      <c r="O1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2">
         <v>287.2007</v>
@@ -853,39 +890,42 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2">
         <v>1.25</v>
       </c>
-      <c r="J2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2">
         <v>0.8</v>
       </c>
-      <c r="L2" t="s">
-        <v>73</v>
-      </c>
       <c r="M2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="N2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>82</v>
+      </c>
+      <c r="O2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>541.2642</v>
@@ -897,39 +937,42 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3">
         <v>1.14</v>
       </c>
-      <c r="J3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3">
         <v>0.71</v>
       </c>
-      <c r="L3" t="s">
-        <v>74</v>
-      </c>
       <c r="M3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>89</v>
+      </c>
+      <c r="O3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>344.2797</v>
@@ -941,248 +984,229 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4">
         <v>0.93</v>
       </c>
-      <c r="J4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4">
         <v>0.73</v>
       </c>
-      <c r="L4" t="s">
-        <v>75</v>
-      </c>
       <c r="M4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>88</v>
+      </c>
+      <c r="O4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D5">
-        <v>158.027</v>
+        <v>558.2914</v>
       </c>
       <c r="E5">
-        <v>1.42</v>
+        <v>10.76</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5">
-        <v>-1.19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5">
-        <v>0.28</v>
-      </c>
-      <c r="L5" t="s">
-        <v>76</v>
+      <c r="I5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5">
+        <v>0.87</v>
+      </c>
+      <c r="K5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5">
+        <v>0.6899999999999999</v>
       </c>
       <c r="M5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>90</v>
+      </c>
+      <c r="O5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D6">
-        <v>558.2914</v>
+        <v>583.2553</v>
       </c>
       <c r="E6">
-        <v>10.76</v>
+        <v>13.48</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>0.87</v>
-      </c>
-      <c r="J6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="L6" t="s">
-        <v>77</v>
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6">
+        <v>2.18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6">
+        <v>0.77</v>
       </c>
       <c r="M6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>91</v>
+      </c>
+      <c r="O6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D7">
-        <v>583.2553</v>
+        <v>496.3397</v>
       </c>
       <c r="E7">
-        <v>13.48</v>
+        <v>16.71</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>2.18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>70</v>
-      </c>
-      <c r="K7">
-        <v>0.77</v>
-      </c>
-      <c r="L7" t="s">
-        <v>78</v>
+      <c r="I7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7">
+        <v>1.3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7">
+        <v>0.79</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>82</v>
+      </c>
+      <c r="O7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>496.3397</v>
+        <v>231.1704</v>
       </c>
       <c r="E8">
-        <v>16.71</v>
+        <v>3.72</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
-      <c r="I8">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8">
-        <v>0.79</v>
-      </c>
-      <c r="L8" t="s">
-        <v>79</v>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8">
+        <v>1.72</v>
+      </c>
+      <c r="K8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8">
+        <v>0.76</v>
       </c>
       <c r="M8" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="N8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9">
-        <v>231.1704</v>
-      </c>
-      <c r="E9">
-        <v>3.72</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="I9">
-        <v>1.72</v>
-      </c>
-      <c r="J9" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9">
-        <v>0.76</v>
-      </c>
-      <c r="L9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M9" t="s">
-        <v>84</v>
-      </c>
-      <c r="N9" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="O8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -177,7 +177,7 @@
     <t>Detected, % Control/BC/PC</t>
   </si>
   <si>
-    <t>C19H28O3 oxo-androstane (putatively 11-oxoetiocholanolone)</t>
+    <t>11-Oxoetiocholanolone glucuronide (putative)</t>
   </si>
   <si>
     <t>Tetrahydrocortisone glucuronide (putative)</t>
@@ -222,7 +222,7 @@
     <t>no</t>
   </si>
   <si>
-    <t>C19H28O3 steroid isomers (e.g., 11-oxoetiocholanolone, 11-oxoandrosterone, 7β-hydroxy-DHEA) not resolved</t>
+    <t>11-oxoetiocholanolone and 11-oxoandrosterone glucuronides (5β/5α) not distinguished; identity assigned from the aglycone MS/MS</t>
   </si>
   <si>
     <t>tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min</t>
@@ -306,7 +306,7 @@
     <t>98/100/100</t>
   </si>
   <si>
-    <t>Isomers: C19H28O3 oxo-androstane (putatively 11-oxoetiocholanolone): C19H28O3 steroid isomers (e.g., 11-oxoetiocholanolone, 11-oxoandrosterone, 7β-hydroxy-DHEA) not resolved; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min; Dodecanoylcarnitine: branched-chain C12 acylcarnitine isomers not excluded; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min; Biliverdin: biliverdin IXα assumed; other IX isomers not resolved; LysoPC(16:0): sn-1/sn-2 regioisomers not resolved; Valyl-Leucine: Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
+    <t>Isomers: 11-Oxoetiocholanolone glucuronide (putative): 11-oxoetiocholanolone and 11-oxoandrosterone glucuronides (5β/5α) not distinguished; identity assigned from the aglycone MS/MS; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min; Dodecanoylcarnitine: branched-chain C12 acylcarnitine isomers not excluded; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min; Biliverdin: biliverdin IXα assumed; other IX isomers not resolved; LysoPC(16:0): sn-1/sn-2 regioisomers not resolved; Valyl-Leucine: Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
   </si>
 </sst>
 </file>

--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="96">
   <si>
     <t>Group</t>
   </si>
@@ -195,16 +195,13 @@
     <t>Valyl-Leucine</t>
   </si>
   <si>
-    <t>5.beta.-Androstan-3.alpha.-ol-11,17-dione</t>
-  </si>
-  <si>
-    <t>NCGC00380230-01_C26H40O9_2,4a,6-Trihydroxy-8-isopropyl-1,1-dimethyl-2,3,4,4a,5,10,11,11a-octahydro-1H-dibenzo[a,d][7]annulen-7-yl beta-D-glucopyranoside</t>
+    <t>5.beta.-Androstan-3.alpha.-ol-11,17-dione (11-oxoetiocholanolone; MS/MS of the aglycone ion)</t>
+  </si>
+  <si>
+    <t>5.beta.-Pregnane-3.alpha.,17,21-triol-11,20-dione (tetrahydrocortisone; MS/MS of the co-eluting aglycone ion)</t>
   </si>
   <si>
     <t>LAUROYLCARNITINE</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>BILIVERDIN</t>
@@ -890,31 +887,31 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J2">
         <v>1.25</v>
       </c>
       <c r="K2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L2">
         <v>0.8</v>
       </c>
       <c r="M2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -937,31 +934,31 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J3">
         <v>1.14</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L3">
         <v>0.71</v>
       </c>
       <c r="M3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -984,31 +981,31 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J4">
         <v>0.93</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L4">
         <v>0.73</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1019,7 +1016,7 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <v>558.2914</v>
@@ -1031,31 +1028,31 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J5">
         <v>0.87</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L5">
         <v>0.6899999999999999</v>
       </c>
       <c r="M5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1066,7 +1063,7 @@
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>583.2553</v>
@@ -1078,31 +1075,31 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J6">
         <v>2.18</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L6">
         <v>0.77</v>
       </c>
       <c r="M6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1113,7 +1110,7 @@
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>496.3397</v>
@@ -1125,31 +1122,31 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J7">
         <v>1.3</v>
       </c>
       <c r="K7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L7">
         <v>0.79</v>
       </c>
       <c r="M7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1160,7 +1157,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>231.1704</v>
@@ -1172,31 +1169,31 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J8">
         <v>1.72</v>
       </c>
       <c r="K8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L8">
         <v>0.76</v>
       </c>
       <c r="M8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1206,7 +1203,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -213,12 +213,12 @@
     <t>Val-Leu</t>
   </si>
   <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>11-oxoetiocholanolone and 11-oxoandrosterone glucuronides (5β/5α) not distinguished; identity assigned from the aglycone MS/MS</t>
   </si>
   <si>
@@ -240,7 +240,7 @@
     <t>Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
   </si>
   <si>
-    <t>6.3e-03</t>
+    <t>5.6e-03</t>
   </si>
   <si>
     <t>1.9e-02</t>
@@ -878,10 +878,10 @@
         <v>59</v>
       </c>
       <c r="D2">
-        <v>287.2007</v>
+        <v>498.2697</v>
       </c>
       <c r="E2">
-        <v>11.06</v>
+        <v>11.05</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -896,13 +896,13 @@
         <v>67</v>
       </c>
       <c r="J2">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="K2" t="s">
         <v>74</v>
       </c>
       <c r="L2">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="s">
         <v>81</v>
@@ -934,7 +934,7 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -1028,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1122,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1169,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H8">
         <v>2</v>

--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="90">
   <si>
     <t>Group</t>
   </si>
@@ -45,7 +45,7 @@
     <t>PC</t>
   </si>
   <si>
-    <t>18/25 (2)</t>
+    <t>19/26 (0)</t>
   </si>
   <si>
     <t>24/5 (0)</t>
@@ -54,7 +54,7 @@
     <t>20/0 (0)</t>
   </si>
   <si>
-    <t>53.3 ± 13.9</t>
+    <t>53.0 ± 14.9</t>
   </si>
   <si>
     <t>62.9 ± 9.7</t>
@@ -63,7 +63,7 @@
     <t>70.7 ± 6.6</t>
   </si>
   <si>
-    <t>58 (25–72)</t>
+    <t>58 (18–72)</t>
   </si>
   <si>
     <t>62 (41–78)</t>
@@ -75,7 +75,7 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Age was not available for 4 participants (4 Control) and sex for 2 (2 Control); 0 lacked both. These participants were retained in the unadjusted analyses (Mann–Whitney U tests, contamination index, cross-validated models on all samples) and excluded from the adjusted linear model (complete-case analysis, n = 88 of 94) and from age- and contamination-matched pairs; missing values were not imputed.</t>
+    <t>Age was not available for 3 participants (3 Control) and sex for 0 (); 0 lacked both. These participants were retained in the unadjusted analyses (Mann–Whitney U tests, contamination index, cross-validated models on all samples) and excluded from the adjusted linear model (complete-case analysis, n = 91 of 94) and from age- and contamination-matched pairs; missing values were not imputed.</t>
   </si>
   <si>
     <t>test</t>
@@ -108,19 +108,19 @@
     <t>age PC vs male controls, Mann–Whitney U</t>
   </si>
   <si>
-    <t>2.3e-06</t>
-  </si>
-  <si>
-    <t>0.0057</t>
-  </si>
-  <si>
-    <t>0.00064</t>
-  </si>
-  <si>
-    <t>1.2e-06</t>
-  </si>
-  <si>
-    <t>3.2e-06</t>
+    <t>3.1e-06</t>
+  </si>
+  <si>
+    <t>0.0067</t>
+  </si>
+  <si>
+    <t>0.00068</t>
+  </si>
+  <si>
+    <t>1.7e-06</t>
+  </si>
+  <si>
+    <t>3.5e-06</t>
   </si>
   <si>
     <t>0.0076</t>
@@ -129,7 +129,7 @@
     <t>0.07</t>
   </si>
   <si>
-    <t>8.2e-05</t>
+    <t>7.7e-05</t>
   </si>
   <si>
     <t>No.</t>
@@ -183,15 +183,12 @@
     <t>Tetrahydrocortisone glucuronide (putative)</t>
   </si>
   <si>
-    <t>Dodecanoylcarnitine</t>
+    <t>LysoPC(16:0)</t>
   </si>
   <si>
     <t>Biliverdin</t>
   </si>
   <si>
-    <t>LysoPC(16:0)</t>
-  </si>
-  <si>
     <t>Valyl-Leucine</t>
   </si>
   <si>
@@ -201,15 +198,12 @@
     <t>5.beta.-Pregnane-3.alpha.,17,21-triol-11,20-dione (tetrahydrocortisone; MS/MS of the co-eluting aglycone ion)</t>
   </si>
   <si>
-    <t>LAUROYLCARNITINE</t>
+    <t>1-Palmitoyl-sn-glycero-3-phosphocholine</t>
   </si>
   <si>
     <t>BILIVERDIN</t>
   </si>
   <si>
-    <t>1-Palmitoyl-sn-glycero-3-phosphocholine</t>
-  </si>
-  <si>
     <t>Val-Leu</t>
   </si>
   <si>
@@ -225,85 +219,73 @@
     <t>tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min</t>
   </si>
   <si>
-    <t>branched-chain C12 acylcarnitine isomers not excluded</t>
+    <t>sn-1/sn-2 regioisomers not resolved</t>
+  </si>
+  <si>
+    <t>biliverdin IXα assumed; other IX isomers not resolved</t>
   </si>
   <si>
     <t>tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min</t>
   </si>
   <si>
-    <t>biliverdin IXα assumed; other IX isomers not resolved</t>
-  </si>
-  <si>
-    <t>sn-1/sn-2 regioisomers not resolved</t>
-  </si>
-  <si>
     <t>Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
   </si>
   <si>
-    <t>5.6e-03</t>
-  </si>
-  <si>
-    <t>1.9e-02</t>
-  </si>
-  <si>
-    <t>2.0e-02</t>
-  </si>
-  <si>
-    <t>2.9e-02</t>
-  </si>
-  <si>
-    <t>4.3e-02</t>
-  </si>
-  <si>
-    <t>4.4e-02</t>
-  </si>
-  <si>
-    <t>4.8e-02</t>
+    <t>5.9e-03</t>
+  </si>
+  <si>
+    <t>2.3e-02</t>
+  </si>
+  <si>
+    <t>3.0e-02</t>
+  </si>
+  <si>
+    <t>3.1e-02</t>
+  </si>
+  <si>
+    <t>3.7e-02</t>
+  </si>
+  <si>
+    <t>3.9e-02</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>0.008</t>
   </si>
   <si>
     <t>0.000</t>
   </si>
   <si>
-    <t>0.011</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
     <t>0.025</t>
   </si>
   <si>
     <t>0.019</t>
   </si>
   <si>
-    <t>0.001</t>
-  </si>
-  <si>
     <t>100/100/100</t>
   </si>
   <si>
-    <t>100/97/100</t>
-  </si>
-  <si>
     <t>89/97/75</t>
   </si>
   <si>
     <t>98/100/100</t>
   </si>
   <si>
-    <t>Isomers: 11-Oxoetiocholanolone glucuronide (putative): 11-oxoetiocholanolone and 11-oxoandrosterone glucuronides (5β/5α) not distinguished; identity assigned from the aglycone MS/MS; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min; Dodecanoylcarnitine: branched-chain C12 acylcarnitine isomers not excluded; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min; Biliverdin: biliverdin IXα assumed; other IX isomers not resolved; LysoPC(16:0): sn-1/sn-2 regioisomers not resolved; Valyl-Leucine: Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
+    <t>Isomers: 11-Oxoetiocholanolone glucuronide (putative): 11-oxoetiocholanolone and 11-oxoandrosterone glucuronides (5β/5α) not distinguished; identity assigned from the aglycone MS/MS; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min; LysoPC(16:0): sn-1/sn-2 regioisomers not resolved; Biliverdin: biliverdin IXα assumed; other IX isomers not resolved; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min; Valyl-Leucine: Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
   </si>
 </sst>
 </file>
@@ -675,7 +657,7 @@
         <v>15</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -817,7 +799,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -875,7 +857,7 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2">
         <v>498.2697</v>
@@ -887,31 +869,31 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J2">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L2">
         <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -922,7 +904,7 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3">
         <v>541.2642</v>
@@ -934,31 +916,31 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L3">
         <v>0.71</v>
       </c>
       <c r="M3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -969,43 +951,43 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4">
-        <v>344.2797</v>
+        <v>496.3397</v>
       </c>
       <c r="E4">
-        <v>14.37</v>
+        <v>16.71</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J4">
-        <v>0.93</v>
+        <v>1.33</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L4">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="M4" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" t="s">
         <v>83</v>
       </c>
-      <c r="N4" t="s">
-        <v>87</v>
-      </c>
       <c r="O4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1013,46 +995,46 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5">
-        <v>558.2914</v>
+        <v>583.2553</v>
       </c>
       <c r="E5">
-        <v>10.76</v>
+        <v>13.48</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J5">
-        <v>0.87</v>
+        <v>2.2</v>
       </c>
       <c r="K5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5">
+        <v>0.77</v>
+      </c>
+      <c r="M5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" t="s">
         <v>77</v>
       </c>
-      <c r="L5">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="M5" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" t="s">
-        <v>89</v>
-      </c>
       <c r="O5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1060,46 +1042,46 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D6">
-        <v>583.2553</v>
+        <v>558.2914</v>
       </c>
       <c r="E6">
-        <v>13.48</v>
+        <v>10.76</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J6">
-        <v>2.18</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L6">
-        <v>0.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M6" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" t="s">
         <v>85</v>
       </c>
-      <c r="N6" t="s">
-        <v>90</v>
-      </c>
       <c r="O6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1110,100 +1092,53 @@
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7">
-        <v>496.3397</v>
+        <v>231.1704</v>
       </c>
       <c r="E7">
-        <v>16.71</v>
+        <v>3.72</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J7">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L7">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="M7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8">
-        <v>231.1704</v>
-      </c>
-      <c r="E8">
-        <v>3.72</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8">
-        <v>1.72</v>
-      </c>
-      <c r="K8" t="s">
-        <v>80</v>
-      </c>
-      <c r="L8">
-        <v>0.76</v>
-      </c>
-      <c r="M8" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -75,7 +75,7 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Age was not available for 3 participants (3 Control) and sex for 0 (); 0 lacked both. These participants were retained in the unadjusted analyses (Mann–Whitney U tests, contamination index, cross-validated models on all samples) and excluded from the adjusted linear model (complete-case analysis, n = 91 of 94) and from age- and contamination-matched pairs; missing values were not imputed.</t>
+    <t>Age was not available for 3 participants (3 Control). These participants were retained in the unadjusted analyses (Mann–Whitney U tests, contamination index, cross-validated models on all samples) and excluded from the adjusted linear model (complete-case analysis, n = 91 of 94) and from age-matched pairs; missing values were not imputed.</t>
   </si>
   <si>
     <t>test</t>

--- a/results/publication/Tables_main.xlsx
+++ b/results/publication/Tables_main.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
   <si>
     <t>Group</t>
   </si>
@@ -54,7 +54,7 @@
     <t>20/0 (0)</t>
   </si>
   <si>
-    <t>53.0 ± 14.9</t>
+    <t>53.3 ± 14.6</t>
   </si>
   <si>
     <t>62.9 ± 9.7</t>
@@ -63,7 +63,7 @@
     <t>70.7 ± 6.6</t>
   </si>
   <si>
-    <t>58 (18–72)</t>
+    <t>59 (18–72)</t>
   </si>
   <si>
     <t>62 (41–78)</t>
@@ -75,7 +75,7 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Age was not available for 3 participants (3 Control). These participants were retained in the unadjusted analyses (Mann–Whitney U tests, contamination index, cross-validated models on all samples) and excluded from the adjusted linear model (complete-case analysis, n = 91 of 94) and from age-matched pairs; missing values were not imputed.</t>
+    <t>Age and sex were available for all participants.</t>
   </si>
   <si>
     <t>test</t>
@@ -108,16 +108,16 @@
     <t>age PC vs male controls, Mann–Whitney U</t>
   </si>
   <si>
-    <t>3.1e-06</t>
-  </si>
-  <si>
-    <t>0.0067</t>
+    <t>2e-06</t>
+  </si>
+  <si>
+    <t>0.0072</t>
   </si>
   <si>
     <t>0.00068</t>
   </si>
   <si>
-    <t>1.7e-06</t>
+    <t>9.2e-07</t>
   </si>
   <si>
     <t>3.5e-06</t>
@@ -183,30 +183,24 @@
     <t>Tetrahydrocortisone glucuronide (putative)</t>
   </si>
   <si>
+    <t>Biliverdin</t>
+  </si>
+  <si>
     <t>LysoPC(16:0)</t>
   </si>
   <si>
-    <t>Biliverdin</t>
-  </si>
-  <si>
-    <t>Valyl-Leucine</t>
-  </si>
-  <si>
     <t>5.beta.-Androstan-3.alpha.-ol-11,17-dione (11-oxoetiocholanolone; MS/MS of the aglycone ion)</t>
   </si>
   <si>
     <t>5.beta.-Pregnane-3.alpha.,17,21-triol-11,20-dione (tetrahydrocortisone; MS/MS of the co-eluting aglycone ion)</t>
   </si>
   <si>
+    <t>BILIVERDIN</t>
+  </si>
+  <si>
     <t>1-Palmitoyl-sn-glycero-3-phosphocholine</t>
   </si>
   <si>
-    <t>BILIVERDIN</t>
-  </si>
-  <si>
-    <t>Val-Leu</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -219,52 +213,43 @@
     <t>tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min</t>
   </si>
   <si>
+    <t>biliverdin IXα assumed; other IX isomers not resolved</t>
+  </si>
+  <si>
     <t>sn-1/sn-2 regioisomers not resolved</t>
   </si>
   <si>
-    <t>biliverdin IXα assumed; other IX isomers not resolved</t>
-  </si>
-  <si>
     <t>tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min</t>
   </si>
   <si>
-    <t>Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
-  </si>
-  <si>
-    <t>5.9e-03</t>
-  </si>
-  <si>
-    <t>2.3e-02</t>
+    <t>4.7e-03</t>
+  </si>
+  <si>
+    <t>1.8e-02</t>
+  </si>
+  <si>
+    <t>2.4e-02</t>
+  </si>
+  <si>
+    <t>2.5e-02</t>
   </si>
   <si>
     <t>3.0e-02</t>
   </si>
   <si>
-    <t>3.1e-02</t>
-  </si>
-  <si>
-    <t>3.7e-02</t>
-  </si>
-  <si>
-    <t>3.9e-02</t>
-  </si>
-  <si>
     <t>0.001</t>
   </si>
   <si>
     <t>0.026</t>
   </si>
   <si>
+    <t>0.042</t>
+  </si>
+  <si>
     <t>0.003</t>
   </si>
   <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>0.008</t>
+    <t>0.024</t>
   </si>
   <si>
     <t>0.000</t>
@@ -282,10 +267,7 @@
     <t>89/97/75</t>
   </si>
   <si>
-    <t>98/100/100</t>
-  </si>
-  <si>
-    <t>Isomers: 11-Oxoetiocholanolone glucuronide (putative): 11-oxoetiocholanolone and 11-oxoandrosterone glucuronides (5β/5α) not distinguished; identity assigned from the aglycone MS/MS; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min; LysoPC(16:0): sn-1/sn-2 regioisomers not resolved; Biliverdin: biliverdin IXα assumed; other IX isomers not resolved; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min; Valyl-Leucine: Leu-Val, Val-Ile and Ile-Val not excluded by MS/MS; in this dataset MS-DIAL also matched Leu-Val (2.68 min) and Val-Leu (3.93 min) at the same m/z</t>
+    <t>Isomers: 11-Oxoetiocholanolone glucuronide (putative): 11-oxoetiocholanolone and 11-oxoandrosterone glucuronides (5β/5α) not distinguished; identity assigned from the aglycone MS/MS; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 10.76 min; Biliverdin: biliverdin IXα assumed; other IX isomers not resolved; LysoPC(16:0): sn-1/sn-2 regioisomers not resolved; Tetrahydrocortisone glucuronide (putative): tetrahydrocortisone/allo-tetrahydrocortisone and 3- vs 21-glucuronide not distinguished; a second isomer elutes at 11.06 min</t>
   </si>
 </sst>
 </file>
@@ -657,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -799,7 +781,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -857,7 +839,7 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>498.2697</v>
@@ -869,31 +851,31 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L2">
         <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="O2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -904,7 +886,7 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3">
         <v>541.2642</v>
@@ -916,31 +898,31 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L3">
         <v>0.71</v>
       </c>
       <c r="M3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="O3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -951,43 +933,43 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4">
-        <v>496.3397</v>
+        <v>583.2553</v>
       </c>
       <c r="E4">
-        <v>16.71</v>
+        <v>13.48</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J4">
-        <v>1.33</v>
+        <v>2.23</v>
       </c>
       <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4">
+        <v>0.77</v>
+      </c>
+      <c r="M4" t="s">
+        <v>75</v>
+      </c>
+      <c r="N4" t="s">
         <v>73</v>
       </c>
-      <c r="L4">
-        <v>0.79</v>
-      </c>
-      <c r="M4" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" t="s">
-        <v>83</v>
-      </c>
       <c r="O4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -998,43 +980,43 @@
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5">
-        <v>583.2553</v>
+        <v>496.3397</v>
       </c>
       <c r="E5">
-        <v>13.48</v>
+        <v>16.71</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J5">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L5">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="M5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1045,7 +1027,7 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6">
         <v>558.2914</v>
@@ -1057,88 +1039,41 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J6">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L6">
         <v>0.6899999999999999</v>
       </c>
       <c r="M6" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" t="s">
+        <v>80</v>
+      </c>
+      <c r="O6" t="s">
         <v>81</v>
       </c>
-      <c r="N6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>231.1704</v>
-      </c>
-      <c r="E7">
-        <v>3.72</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7">
-        <v>1.68</v>
-      </c>
-      <c r="K7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L7">
-        <v>0.76</v>
-      </c>
-      <c r="M7" t="s">
-        <v>82</v>
-      </c>
-      <c r="N7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O7" t="s">
-        <v>88</v>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
